--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104726_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104726_W30.xlsx
@@ -553,7 +553,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>A. LEN</t>
+          <t>S. LLULL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -565,64 +565,64 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3108</v>
+        <v>4.7843</v>
       </c>
       <c r="E2" t="n">
-        <v>3.5483</v>
+        <v>4.9398</v>
       </c>
       <c r="F2" t="n">
-        <v>1.7625</v>
+        <v>-0.1555</v>
       </c>
       <c r="G2" t="n">
-        <v>3.1306</v>
+        <v>1.544</v>
       </c>
       <c r="H2" t="n">
-        <v>2.1233</v>
+        <v>-1.2783</v>
       </c>
       <c r="I2" t="n">
-        <v>1.0073</v>
+        <v>2.8223</v>
       </c>
       <c r="J2" t="n">
-        <v>3.1973</v>
+        <v>2.9182</v>
       </c>
       <c r="K2" t="n">
-        <v>3.1227</v>
+        <v>0.2306</v>
       </c>
       <c r="L2" t="n">
-        <v>0.0746</v>
+        <v>2.6876</v>
       </c>
       <c r="M2" t="n">
-        <v>-0.06660000000000001</v>
+        <v>-1.3742</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.9994</v>
+        <v>-1.5089</v>
       </c>
       <c r="O2" t="n">
-        <v>0.9327</v>
+        <v>0.1347</v>
       </c>
       <c r="P2" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R2" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S2" t="n">
-        <v>1.861</v>
+        <v>0.1312</v>
       </c>
       <c r="T2" t="n">
-        <v>1.395</v>
+        <v>0.2783</v>
       </c>
       <c r="U2" t="n">
-        <v>0.466</v>
+        <v>-0.1471</v>
       </c>
       <c r="V2" t="n">
-        <v>0.092</v>
+        <v>2.8814</v>
       </c>
       <c r="W2" t="n">
-        <v>0.092</v>
+        <v>2.8814</v>
       </c>
       <c r="X2" t="n">
         <v>0</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>S. LLULL</t>
+          <t>A. LEN</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,64 +643,64 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2581</v>
+        <v>3.5893</v>
       </c>
       <c r="E3" t="n">
-        <v>3.7142</v>
+        <v>2.3404</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.456</v>
+        <v>1.2489</v>
       </c>
       <c r="G3" t="n">
-        <v>1.5463</v>
+        <v>3.1278</v>
       </c>
       <c r="H3" t="n">
-        <v>-1.2811</v>
+        <v>2.1173</v>
       </c>
       <c r="I3" t="n">
-        <v>2.8274</v>
+        <v>1.0104</v>
       </c>
       <c r="J3" t="n">
-        <v>2.9343</v>
+        <v>3.1836</v>
       </c>
       <c r="K3" t="n">
-        <v>0.2367</v>
+        <v>3.1091</v>
       </c>
       <c r="L3" t="n">
-        <v>2.6975</v>
+        <v>0.0745</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.388</v>
+        <v>-0.0558</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.5178</v>
+        <v>-0.9918</v>
       </c>
       <c r="O3" t="n">
-        <v>0.1298</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P3" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q3" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R3" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S3" t="n">
-        <v>-1.4029</v>
+        <v>0.1476</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.9717</v>
+        <v>0.2086</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.4312</v>
+        <v>-0.0611</v>
       </c>
       <c r="V3" t="n">
-        <v>2.8875</v>
+        <v>0.0863</v>
       </c>
       <c r="W3" t="n">
-        <v>2.8875</v>
+        <v>0.0863</v>
       </c>
       <c r="X3" t="n">
         <v>0</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>I. ALMANSA</t>
+          <t>M. HEZONJA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.0795</v>
+        <v>0.7746</v>
       </c>
       <c r="E4" t="n">
-        <v>4.3014</v>
+        <v>-0.1073</v>
       </c>
       <c r="F4" t="n">
-        <v>-2.2219</v>
+        <v>0.8819</v>
       </c>
       <c r="G4" t="n">
-        <v>-3.4512</v>
+        <v>3.3968</v>
       </c>
       <c r="H4" t="n">
-        <v>-2.2728</v>
+        <v>0.8185</v>
       </c>
       <c r="I4" t="n">
-        <v>-1.1783</v>
+        <v>2.5783</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1155</v>
+        <v>3.9265</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.973</v>
+        <v>1.9683</v>
       </c>
       <c r="L4" t="n">
-        <v>0.8575</v>
+        <v>1.9582</v>
       </c>
       <c r="M4" t="n">
-        <v>-3.3357</v>
+        <v>-0.5296</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.2999</v>
+        <v>-1.1497</v>
       </c>
       <c r="O4" t="n">
-        <v>-2.0358</v>
+        <v>0.6201</v>
       </c>
       <c r="P4" t="n">
-        <v>1.1359</v>
+        <v>-3.1868</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.2272</v>
+        <v>-4.5526</v>
       </c>
       <c r="R4" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S4" t="n">
-        <v>2.3214</v>
+        <v>0.0199</v>
       </c>
       <c r="T4" t="n">
-        <v>2.4615</v>
+        <v>-0.0258</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.1402</v>
+        <v>0.0457</v>
       </c>
       <c r="V4" t="n">
-        <v>2.0734</v>
+        <v>0.5447</v>
       </c>
       <c r="W4" t="n">
-        <v>2.1825</v>
+        <v>0.5447</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.1091</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M. HEZONJA</t>
+          <t>I. ALMANSA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1139</v>
+        <v>0.7557</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.0327</v>
+        <v>2.7745</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1466</v>
+        <v>-2.0188</v>
       </c>
       <c r="G5" t="n">
-        <v>3.4</v>
+        <v>-3.4441</v>
       </c>
       <c r="H5" t="n">
-        <v>0.819</v>
+        <v>-2.2692</v>
       </c>
       <c r="I5" t="n">
-        <v>2.5811</v>
+        <v>-1.1749</v>
       </c>
       <c r="J5" t="n">
-        <v>3.94</v>
+        <v>-0.1195</v>
       </c>
       <c r="K5" t="n">
-        <v>1.9761</v>
+        <v>-0.976</v>
       </c>
       <c r="L5" t="n">
-        <v>1.9639</v>
+        <v>0.8564000000000001</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.54</v>
+        <v>-3.3246</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1571</v>
+        <v>-1.2932</v>
       </c>
       <c r="O5" t="n">
-        <v>0.6171</v>
+        <v>-2.0314</v>
       </c>
       <c r="P5" t="n">
-        <v>-3.1806</v>
+        <v>1.1382</v>
       </c>
       <c r="Q5" t="n">
-        <v>-4.5437</v>
+        <v>-0.2276</v>
       </c>
       <c r="R5" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S5" t="n">
-        <v>0.3489</v>
+        <v>0.9917</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0254</v>
+        <v>0.9427</v>
       </c>
       <c r="U5" t="n">
-        <v>0.3235</v>
+        <v>0.049</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5456</v>
+        <v>2.07</v>
       </c>
       <c r="W5" t="n">
-        <v>0.5456</v>
+        <v>2.1789</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="6">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7181</v>
+        <v>-0.6095</v>
       </c>
       <c r="E6" t="n">
-        <v>0.6727</v>
+        <v>0.6129</v>
       </c>
       <c r="F6" t="n">
-        <v>-1.3908</v>
+        <v>-1.2224</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.3128</v>
+        <v>-1.3123</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.2915</v>
+        <v>-0.2902</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0212</v>
+        <v>-1.022</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8744</v>
+        <v>0.8663</v>
       </c>
       <c r="K6" t="n">
-        <v>0.6627</v>
+        <v>0.6583</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2117</v>
+        <v>0.2081</v>
       </c>
       <c r="M6" t="n">
-        <v>-2.1872</v>
+        <v>-2.1786</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.9543</v>
+        <v>-0.9485</v>
       </c>
       <c r="O6" t="n">
-        <v>-1.2329</v>
+        <v>-1.2301</v>
       </c>
       <c r="P6" t="n">
-        <v>1.1359</v>
+        <v>1.1382</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R6" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4322</v>
+        <v>-0.3265</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0254</v>
+        <v>-0.0258</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.4576</v>
+        <v>-0.3006</v>
       </c>
       <c r="V6" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>-0.1091</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="7">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3942</v>
+        <v>-1.4083</v>
       </c>
       <c r="E7" t="n">
-        <v>0.6273</v>
+        <v>0.6879</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0215</v>
+        <v>-2.0961</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.6945</v>
+        <v>-0.6885</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.0859</v>
+        <v>-0.0848</v>
       </c>
       <c r="J7" t="n">
-        <v>1.8072</v>
+        <v>1.8031</v>
       </c>
       <c r="K7" t="n">
-        <v>0.1728</v>
+        <v>0.1724</v>
       </c>
       <c r="L7" t="n">
-        <v>1.6344</v>
+        <v>1.6308</v>
       </c>
       <c r="M7" t="n">
-        <v>-2.5017</v>
+        <v>-2.4916</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7814</v>
+        <v>-0.7761</v>
       </c>
       <c r="O7" t="n">
-        <v>-1.7203</v>
+        <v>-1.7155</v>
       </c>
       <c r="P7" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.0625</v>
+        <v>-0.0871</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.044</v>
+        <v>0.0229</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.0185</v>
+        <v>-0.11</v>
       </c>
       <c r="V7" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8603</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-0.8643999999999999</v>
+        <v>-0.8603</v>
       </c>
     </row>
     <row r="8">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.0111</v>
+        <v>-1.5315</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7583</v>
+        <v>1.1011</v>
       </c>
       <c r="F8" t="n">
-        <v>-2.7694</v>
+        <v>-2.6326</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.9348</v>
+        <v>-0.9359</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.5447</v>
+        <v>-0.5455</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.3901</v>
+        <v>-0.3903</v>
       </c>
       <c r="J8" t="n">
-        <v>1.0645</v>
+        <v>1.0559</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0639</v>
+        <v>0.0582</v>
       </c>
       <c r="L8" t="n">
-        <v>1.0006</v>
+        <v>0.9977</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.9994</v>
+        <v>-1.9918</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.6086</v>
+        <v>-0.6037</v>
       </c>
       <c r="O8" t="n">
-        <v>-1.3907</v>
+        <v>-1.3881</v>
       </c>
       <c r="P8" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q8" t="n">
-        <v>-0.2272</v>
+        <v>-0.2276</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9087</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-1.1031</v>
+        <v>-0.6249</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6247</v>
+        <v>-0.272</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.4784</v>
+        <v>-0.3529</v>
       </c>
       <c r="V8" t="n">
-        <v>-0.6548</v>
+        <v>-0.6536999999999999</v>
       </c>
       <c r="W8" t="n">
-        <v>0.5456</v>
+        <v>0.5447</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2004</v>
+        <v>-1.1984</v>
       </c>
     </row>
     <row r="9">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.7438</v>
+        <v>-1.8552</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.7034</v>
+        <v>-1.0516</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.0404</v>
+        <v>-0.8035</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.049</v>
+        <v>-1.0408</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.103</v>
+        <v>-0.0983</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.946</v>
+        <v>-0.9425</v>
       </c>
       <c r="J9" t="n">
-        <v>0.106</v>
+        <v>0.1033</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7085</v>
+        <v>0.7067</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6025</v>
+        <v>-0.6035</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.155</v>
+        <v>-1.1441</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8115</v>
+        <v>-0.805</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3435</v>
+        <v>-0.3391</v>
       </c>
       <c r="P9" t="n">
-        <v>0.2272</v>
+        <v>0.2276</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R9" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.9902</v>
+        <v>-0.1103</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.8329</v>
+        <v>-0.1745</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1573</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9318</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1594</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>T. LYLES</t>
+          <t>A. FELIZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-3.5345</v>
+        <v>-3.1492</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.8097</v>
+        <v>0.3128</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.7248</v>
+        <v>-3.4619</v>
       </c>
       <c r="G10" t="n">
-        <v>-2.3935</v>
+        <v>-1.0491</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.8017</v>
+        <v>0.7729</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.5918</v>
+        <v>-1.822</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.1461</v>
+        <v>0.6268</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6860000000000001</v>
+        <v>1.6925</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-1.0656</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.2473</v>
+        <v>-1.6759</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.4877</v>
+        <v>-0.9196</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P10" t="n">
-        <v>-3.4078</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q10" t="n">
-        <v>-4.7709</v>
+        <v>-1.3658</v>
       </c>
       <c r="R10" t="n">
-        <v>1.3631</v>
+        <v>0.4553</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.1254</v>
+        <v>1.4853</v>
       </c>
       <c r="T10" t="n">
-        <v>0.6061</v>
+        <v>0.894</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.7315</v>
+        <v>0.5914</v>
       </c>
       <c r="V10" t="n">
-        <v>2.3922</v>
+        <v>-2.6749</v>
       </c>
       <c r="W10" t="n">
-        <v>2.5013</v>
+        <v>0.1578</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.1091</v>
+        <v>-2.8326</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FELIZ</t>
+          <t>T. LYLES</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-3.592</v>
+        <v>-3.2599</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3323</v>
+        <v>-1.7684</v>
       </c>
       <c r="F11" t="n">
-        <v>-3.2597</v>
+        <v>-1.4915</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.0461</v>
+        <v>-2.3922</v>
       </c>
       <c r="H11" t="n">
-        <v>0.7754</v>
+        <v>-0.8013</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.8215</v>
+        <v>-1.5909</v>
       </c>
       <c r="J11" t="n">
-        <v>0.6377</v>
+        <v>-0.1558</v>
       </c>
       <c r="K11" t="n">
-        <v>1.6996</v>
+        <v>0.6787</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.0619</v>
+        <v>-0.8345</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.6838</v>
+        <v>-2.2364</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.9242</v>
+        <v>-1.48</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.7563</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9087</v>
+        <v>-3.4145</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.3631</v>
+        <v>-4.7803</v>
       </c>
       <c r="R11" t="n">
-        <v>0.4544</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>1.0406</v>
+        <v>0.1612</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2336</v>
+        <v>0.6731</v>
       </c>
       <c r="U11" t="n">
-        <v>0.8070000000000001</v>
+        <v>-0.5119</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.6778</v>
+        <v>2.3855</v>
       </c>
       <c r="W11" t="n">
-        <v>0.1594</v>
+        <v>2.4945</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.8373</v>
+        <v>-0.1089</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.9247</v>
+        <v>-4.5613</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.9966</v>
+        <v>-5.5845</v>
       </c>
       <c r="F12" t="n">
-        <v>1.0718</v>
+        <v>1.0231</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.8017</v>
+        <v>-1.7975</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.5568</v>
+        <v>-0.552</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.2449</v>
+        <v>-1.2455</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.8947</v>
+        <v>-1.898</v>
       </c>
       <c r="K12" t="n">
-        <v>0.3975</v>
+        <v>0.3964</v>
       </c>
       <c r="L12" t="n">
-        <v>-2.2921</v>
+        <v>-2.2945</v>
       </c>
       <c r="M12" t="n">
-        <v>0.093</v>
+        <v>0.1005</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.9543</v>
+        <v>-0.9485</v>
       </c>
       <c r="O12" t="n">
-        <v>1.0472</v>
+        <v>1.049</v>
       </c>
       <c r="P12" t="n">
-        <v>-2.0447</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q12" t="n">
-        <v>-3.4078</v>
+        <v>-3.4145</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.5574</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.6941000000000001</v>
+        <v>-0.272</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.2249</v>
+        <v>-0.2854</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-7.156099999999999</v>
+        <v>-6.471</v>
       </c>
       <c r="E13" t="n">
-        <v>3.7475</v>
+        <v>4.257599999999998</v>
       </c>
       <c r="F13" t="n">
-        <v>-10.9036</v>
+        <v>-10.7284</v>
       </c>
       <c r="G13" t="n">
-        <v>-4.6067</v>
+        <v>-4.591800000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>-2.7425</v>
+        <v>-2.7298</v>
       </c>
       <c r="I13" t="n">
-        <v>-1.8639</v>
+        <v>-1.8619</v>
       </c>
       <c r="J13" t="n">
-        <v>12.4051</v>
+        <v>12.3104</v>
       </c>
       <c r="K13" t="n">
-        <v>8.753500000000001</v>
+        <v>8.6952</v>
       </c>
       <c r="L13" t="n">
-        <v>3.6515</v>
+        <v>3.615200000000001</v>
       </c>
       <c r="M13" t="n">
-        <v>-17.0117</v>
+        <v>-16.9021</v>
       </c>
       <c r="N13" t="n">
-        <v>-11.4962</v>
+        <v>-11.425</v>
       </c>
       <c r="O13" t="n">
-        <v>-5.5156</v>
+        <v>-5.477</v>
       </c>
       <c r="P13" t="n">
-        <v>-5.679600000000001</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="Q13" t="n">
-        <v>-19.3107</v>
+        <v>-19.3488</v>
       </c>
       <c r="R13" t="n">
-        <v>13.631</v>
+        <v>13.658</v>
       </c>
       <c r="S13" t="n">
-        <v>0.5367</v>
+        <v>1.2307</v>
       </c>
       <c r="T13" t="n">
-        <v>1.5796</v>
+        <v>2.249499999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-1.0431</v>
+        <v>-1.0187</v>
       </c>
       <c r="V13" t="n">
-        <v>2.5934</v>
+        <v>2.5806</v>
       </c>
       <c r="W13" t="n">
-        <v>9.0733</v>
+        <v>9.046099999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-6.4801</v>
+        <v>-6.465299999999999</v>
       </c>
     </row>
     <row r="14">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>4.3524</v>
+        <v>4.8135</v>
       </c>
       <c r="E14" t="n">
-        <v>5.4083</v>
+        <v>6.0966</v>
       </c>
       <c r="F14" t="n">
-        <v>-1.0559</v>
+        <v>-1.2831</v>
       </c>
       <c r="G14" t="n">
-        <v>2.0842</v>
+        <v>2.0862</v>
       </c>
       <c r="H14" t="n">
-        <v>1.1262</v>
+        <v>1.1283</v>
       </c>
       <c r="I14" t="n">
-        <v>0.958</v>
+        <v>0.9579</v>
       </c>
       <c r="J14" t="n">
-        <v>4.2421</v>
+        <v>4.2315</v>
       </c>
       <c r="K14" t="n">
-        <v>1.6072</v>
+        <v>1.603</v>
       </c>
       <c r="L14" t="n">
-        <v>2.635</v>
+        <v>2.6285</v>
       </c>
       <c r="M14" t="n">
-        <v>-2.1579</v>
+        <v>-2.1453</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.4809</v>
+        <v>-0.4747</v>
       </c>
       <c r="O14" t="n">
-        <v>-1.677</v>
+        <v>-1.6706</v>
       </c>
       <c r="P14" t="n">
-        <v>1.5903</v>
+        <v>1.5934</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R14" t="n">
-        <v>2.7262</v>
+        <v>2.7316</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.5047</v>
+        <v>-1.0451</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.9717</v>
+        <v>-0.2652</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.533</v>
+        <v>-0.7799</v>
       </c>
       <c r="V14" t="n">
-        <v>2.1825</v>
+        <v>2.1789</v>
       </c>
       <c r="W14" t="n">
-        <v>3.2738</v>
+        <v>3.2684</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.0913</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="15">
@@ -1579,67 +1579,67 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>4.2306</v>
+        <v>4.6168</v>
       </c>
       <c r="E15" t="n">
-        <v>3.979</v>
+        <v>4.1948</v>
       </c>
       <c r="F15" t="n">
-        <v>0.2516</v>
+        <v>0.422</v>
       </c>
       <c r="G15" t="n">
-        <v>3.9674</v>
+        <v>3.9592</v>
       </c>
       <c r="H15" t="n">
-        <v>3.0873</v>
+        <v>3.0821</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8801</v>
+        <v>0.877</v>
       </c>
       <c r="J15" t="n">
-        <v>5.7396</v>
+        <v>5.7234</v>
       </c>
       <c r="K15" t="n">
-        <v>4.3722</v>
+        <v>4.3609</v>
       </c>
       <c r="L15" t="n">
-        <v>1.3674</v>
+        <v>1.3624</v>
       </c>
       <c r="M15" t="n">
-        <v>-1.7722</v>
+        <v>-1.7642</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.2848</v>
+        <v>-1.2788</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.4873</v>
+        <v>-0.4854</v>
       </c>
       <c r="P15" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="Q15" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R15" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.8046</v>
+        <v>-0.4122</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.6247</v>
+        <v>-0.3904</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.18</v>
+        <v>-0.0218</v>
       </c>
       <c r="V15" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W15" t="n">
         <v>0</v>
       </c>
       <c r="X15" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
     </row>
     <row r="16">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.4621</v>
+        <v>2.1878</v>
       </c>
       <c r="E16" t="n">
-        <v>2.1089</v>
+        <v>2.0967</v>
       </c>
       <c r="F16" t="n">
-        <v>0.3532</v>
+        <v>0.0911</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.6522</v>
+        <v>-0.6509</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.4598</v>
+        <v>-0.457</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.1924</v>
+        <v>-0.1939</v>
       </c>
       <c r="J16" t="n">
-        <v>1.0616</v>
+        <v>1.054</v>
       </c>
       <c r="K16" t="n">
-        <v>0.9678</v>
+        <v>0.9653</v>
       </c>
       <c r="L16" t="n">
-        <v>0.0939</v>
+        <v>0.0887</v>
       </c>
       <c r="M16" t="n">
-        <v>-1.7139</v>
+        <v>-1.7048</v>
       </c>
       <c r="N16" t="n">
-        <v>-1.4276</v>
+        <v>-1.4223</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.2863</v>
+        <v>-0.2826</v>
       </c>
       <c r="P16" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="Q16" t="n">
         <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6834</v>
+        <v>0.403</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.044</v>
+        <v>-0.0468</v>
       </c>
       <c r="U16" t="n">
-        <v>0.7274</v>
+        <v>0.4498</v>
       </c>
       <c r="V16" t="n">
-        <v>0.3862</v>
+        <v>0.387</v>
       </c>
       <c r="W16" t="n">
-        <v>1.0913</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.705</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="17">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.748</v>
+        <v>1.5002</v>
       </c>
       <c r="E17" t="n">
-        <v>0.6393</v>
+        <v>0.6239</v>
       </c>
       <c r="F17" t="n">
-        <v>1.1087</v>
+        <v>0.8764</v>
       </c>
       <c r="G17" t="n">
-        <v>2.1325</v>
+        <v>2.1316</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.9332</v>
+        <v>-0.9308</v>
       </c>
       <c r="I17" t="n">
-        <v>3.0657</v>
+        <v>3.0624</v>
       </c>
       <c r="J17" t="n">
-        <v>2.8163</v>
+        <v>2.8076</v>
       </c>
       <c r="K17" t="n">
-        <v>0.6973</v>
+        <v>0.6927</v>
       </c>
       <c r="L17" t="n">
-        <v>2.119</v>
+        <v>2.1148</v>
       </c>
       <c r="M17" t="n">
-        <v>-0.6838</v>
+        <v>-0.6758999999999999</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.6305</v>
+        <v>-1.6235</v>
       </c>
       <c r="O17" t="n">
-        <v>0.9467</v>
+        <v>0.9476</v>
       </c>
       <c r="P17" t="n">
-        <v>-0.9087</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q17" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R17" t="n">
-        <v>1.3631</v>
+        <v>1.3658</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8431</v>
+        <v>0.5947</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0948</v>
+        <v>0.0926</v>
       </c>
       <c r="U17" t="n">
-        <v>0.7482</v>
+        <v>0.5021</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
       <c r="W17" t="n">
         <v>0</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="18">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.1706</v>
+        <v>1.0574</v>
       </c>
       <c r="E18" t="n">
-        <v>0.0786</v>
+        <v>-0.4271</v>
       </c>
       <c r="F18" t="n">
-        <v>1.0919</v>
+        <v>1.4845</v>
       </c>
       <c r="G18" t="n">
-        <v>2.9548</v>
+        <v>2.9455</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.7859</v>
+        <v>-1.7913</v>
       </c>
       <c r="I18" t="n">
-        <v>4.7407</v>
+        <v>4.7367</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5574</v>
+        <v>2.5395</v>
       </c>
       <c r="K18" t="n">
-        <v>-1.6807</v>
+        <v>-1.6902</v>
       </c>
       <c r="L18" t="n">
-        <v>4.2381</v>
+        <v>4.2297</v>
       </c>
       <c r="M18" t="n">
-        <v>0.3974</v>
+        <v>0.406</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.1052</v>
+        <v>-0.1011</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5026</v>
+        <v>0.5071</v>
       </c>
       <c r="P18" t="n">
-        <v>-2.4991</v>
+        <v>-2.5039</v>
       </c>
       <c r="Q18" t="n">
-        <v>-4.5437</v>
+        <v>-4.5526</v>
       </c>
       <c r="R18" t="n">
-        <v>2.0447</v>
+        <v>2.0487</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.217</v>
+        <v>-0.3159</v>
       </c>
       <c r="T18" t="n">
-        <v>0.8143</v>
+        <v>0.3388</v>
       </c>
       <c r="U18" t="n">
-        <v>-1.0313</v>
+        <v>-0.6546</v>
       </c>
       <c r="V18" t="n">
-        <v>0.9318</v>
+        <v>0.9317</v>
       </c>
       <c r="W18" t="n">
-        <v>1.2507</v>
+        <v>1.2472</v>
       </c>
       <c r="X18" t="n">
-        <v>-0.3188</v>
+        <v>-0.3155</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>B. DIBBA</t>
+          <t>D. BRANKOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>0.6568000000000001</v>
+        <v>1.0147</v>
       </c>
       <c r="E19" t="n">
-        <v>1.0438</v>
+        <v>-0.4537</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.387</v>
+        <v>1.4684</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.075</v>
+        <v>-1.1365</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2871</v>
+        <v>1.235</v>
       </c>
       <c r="I19" t="n">
-        <v>-1.3621</v>
+        <v>-2.3716</v>
       </c>
       <c r="J19" t="n">
-        <v>0.602</v>
+        <v>-0.0911</v>
       </c>
       <c r="K19" t="n">
-        <v>1.2045</v>
+        <v>2.0544</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.6025</v>
+        <v>-2.1455</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.677</v>
+        <v>-1.0455</v>
       </c>
       <c r="N19" t="n">
-        <v>0.08260000000000001</v>
+        <v>-0.8194</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.7596000000000001</v>
+        <v>-0.226</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1359</v>
+        <v>2.7316</v>
       </c>
       <c r="Q19" t="n">
         <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.1359</v>
+        <v>2.7316</v>
       </c>
       <c r="S19" t="n">
-        <v>0.6871</v>
+        <v>-0.4226</v>
       </c>
       <c r="T19" t="n">
-        <v>0.4419</v>
+        <v>-0.3627</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2453</v>
+        <v>-0.06</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.0913</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>D. BRANKOVIC</t>
+          <t>A. KURUCS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.5345</v>
+        <v>0.83</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.9134</v>
+        <v>-1.7625</v>
       </c>
       <c r="F20" t="n">
-        <v>1.4479</v>
+        <v>2.5926</v>
       </c>
       <c r="G20" t="n">
-        <v>-1.1361</v>
+        <v>-0.3584</v>
       </c>
       <c r="H20" t="n">
-        <v>1.236</v>
+        <v>-0.4598</v>
       </c>
       <c r="I20" t="n">
-        <v>-2.372</v>
+        <v>0.1014</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.0805</v>
+        <v>-0.3314</v>
       </c>
       <c r="K20" t="n">
-        <v>2.0625</v>
+        <v>0.5031</v>
       </c>
       <c r="L20" t="n">
-        <v>-2.143</v>
+        <v>-0.8345</v>
       </c>
       <c r="M20" t="n">
-        <v>-1.0555</v>
+        <v>-0.027</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.8265</v>
+        <v>-0.9629</v>
       </c>
       <c r="O20" t="n">
-        <v>-0.229</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P20" t="n">
-        <v>2.7262</v>
+        <v>1.8211</v>
       </c>
       <c r="Q20" t="n">
-        <v>0</v>
+        <v>-1.1382</v>
       </c>
       <c r="R20" t="n">
-        <v>2.7262</v>
+        <v>2.9592</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.8962</v>
+        <v>-0.4749</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.8329</v>
+        <v>-0.2929</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0634</v>
+        <v>-0.1819</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1594</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>A. KURUCS</t>
+          <t>B. DIBBA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.2545</v>
+        <v>0.441</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.2244</v>
+        <v>1.0335</v>
       </c>
       <c r="F21" t="n">
-        <v>2.4789</v>
+        <v>-0.5926</v>
       </c>
       <c r="G21" t="n">
-        <v>-0.3616</v>
+        <v>-0.07820000000000001</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.4621</v>
+        <v>1.2816</v>
       </c>
       <c r="I21" t="n">
-        <v>0.1005</v>
+        <v>-1.3598</v>
       </c>
       <c r="J21" t="n">
-        <v>-0.325</v>
+        <v>0.5924</v>
       </c>
       <c r="K21" t="n">
-        <v>0.5072</v>
+        <v>1.1958</v>
       </c>
       <c r="L21" t="n">
-        <v>-0.8322000000000001</v>
+        <v>-0.6035</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0366</v>
+        <v>-0.6706</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.9693000000000001</v>
+        <v>0.0857</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9327</v>
+        <v>-0.7563</v>
       </c>
       <c r="P21" t="n">
-        <v>1.8175</v>
+        <v>1.1382</v>
       </c>
       <c r="Q21" t="n">
-        <v>-1.1359</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>2.9534</v>
+        <v>1.1382</v>
       </c>
       <c r="S21" t="n">
-        <v>-1.042</v>
+        <v>0.4705</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.7635</v>
+        <v>0.4411</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2785</v>
+        <v>0.0294</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
       <c r="W21" t="n">
         <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.1594</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="22">
@@ -2125,40 +2125,40 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.8919</v>
+        <v>-1.0941</v>
       </c>
       <c r="E22" t="n">
-        <v>0.7392</v>
+        <v>0.5023</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.6311</v>
+        <v>-1.5964</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.0172</v>
+        <v>-1.015</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3088</v>
+        <v>-0.3075</v>
       </c>
       <c r="I22" t="n">
-        <v>-0.7083</v>
+        <v>-0.7075</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0891</v>
+        <v>0.08890000000000001</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0518</v>
+        <v>0.0517</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M22" t="n">
-        <v>-1.1063</v>
+        <v>-1.1039</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.3607</v>
+        <v>-0.3592</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.7456</v>
+        <v>-0.7447</v>
       </c>
       <c r="P22" t="n">
         <v>0</v>
@@ -2170,22 +2170,22 @@
         <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>0.6709000000000001</v>
+        <v>0.4656</v>
       </c>
       <c r="T22" t="n">
-        <v>0.6501</v>
+        <v>0.4133</v>
       </c>
       <c r="U22" t="n">
-        <v>0.0208</v>
+        <v>0.0523</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.5456</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="23">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.4169</v>
+        <v>-2.3048</v>
       </c>
       <c r="E23" t="n">
-        <v>1.1397</v>
+        <v>0.1747</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.5565</v>
+        <v>-2.4795</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.1453</v>
+        <v>-2.1477</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.2825</v>
+        <v>-1.2886</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.8628</v>
+        <v>-0.8591</v>
       </c>
       <c r="J23" t="n">
-        <v>-0.2615</v>
+        <v>-0.2717</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.3733</v>
+        <v>-0.3834</v>
       </c>
       <c r="L23" t="n">
-        <v>0.1118</v>
+        <v>0.1117</v>
       </c>
       <c r="M23" t="n">
-        <v>-1.8838</v>
+        <v>-1.8759</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.9092</v>
+        <v>-0.9052</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.9746</v>
+        <v>-0.9708</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1359</v>
+        <v>-1.1382</v>
       </c>
       <c r="R23" t="n">
-        <v>0.6816</v>
+        <v>0.6829</v>
       </c>
       <c r="S23" t="n">
-        <v>1.569</v>
+        <v>0.6851</v>
       </c>
       <c r="T23" t="n">
-        <v>1.6726</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1036</v>
+        <v>-0.0392</v>
       </c>
       <c r="V23" t="n">
-        <v>-0.3862</v>
+        <v>-0.387</v>
       </c>
       <c r="W23" t="n">
-        <v>0.8643999999999999</v>
+        <v>0.8603</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2507</v>
+        <v>-1.2472</v>
       </c>
     </row>
     <row r="24">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.9445</v>
+        <v>-5.8944</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.0952</v>
+        <v>-1.3506</v>
       </c>
       <c r="F24" t="n">
-        <v>-4.8493</v>
+        <v>-4.5439</v>
       </c>
       <c r="G24" t="n">
-        <v>-1.1451</v>
+        <v>-1.144</v>
       </c>
       <c r="H24" t="n">
-        <v>1.2382</v>
+        <v>1.2378</v>
       </c>
       <c r="I24" t="n">
-        <v>-2.3833</v>
+        <v>-2.3818</v>
       </c>
       <c r="J24" t="n">
-        <v>0.5705</v>
+        <v>0.5592</v>
       </c>
       <c r="K24" t="n">
-        <v>2.0798</v>
+        <v>2.0717</v>
       </c>
       <c r="L24" t="n">
-        <v>-1.5092</v>
+        <v>-1.5125</v>
       </c>
       <c r="M24" t="n">
-        <v>-1.7157</v>
+        <v>-1.7032</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.8416</v>
+        <v>-0.8339</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.8741</v>
+        <v>-0.8694</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.4544</v>
+        <v>-0.4553</v>
       </c>
       <c r="Q24" t="n">
-        <v>-2.2719</v>
+        <v>-2.2763</v>
       </c>
       <c r="R24" t="n">
-        <v>1.8175</v>
+        <v>1.8211</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.5256</v>
+        <v>-0.4819</v>
       </c>
       <c r="T24" t="n">
-        <v>0.6061</v>
+        <v>0.3665</v>
       </c>
       <c r="U24" t="n">
-        <v>-1.1317</v>
+        <v>-0.8485</v>
       </c>
       <c r="V24" t="n">
-        <v>-3.8194</v>
+        <v>-3.8132</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-3.8194</v>
+        <v>-3.8132</v>
       </c>
     </row>
     <row r="25">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>7.1562</v>
+        <v>7.168099999999996</v>
       </c>
       <c r="E25" t="n">
-        <v>10.9038</v>
+        <v>10.7286</v>
       </c>
       <c r="F25" t="n">
-        <v>-3.7476</v>
+        <v>-3.5605</v>
       </c>
       <c r="G25" t="n">
-        <v>4.6064</v>
+        <v>4.591799999999999</v>
       </c>
       <c r="H25" t="n">
-        <v>2.7425</v>
+        <v>2.7298</v>
       </c>
       <c r="I25" t="n">
-        <v>1.8641</v>
+        <v>1.861699999999999</v>
       </c>
       <c r="J25" t="n">
-        <v>17.0116</v>
+        <v>16.9023</v>
       </c>
       <c r="K25" t="n">
-        <v>11.4963</v>
+        <v>11.425</v>
       </c>
       <c r="L25" t="n">
-        <v>5.5156</v>
+        <v>5.477</v>
       </c>
       <c r="M25" t="n">
-        <v>-12.4053</v>
+        <v>-12.3103</v>
       </c>
       <c r="N25" t="n">
-        <v>-8.7537</v>
+        <v>-8.6953</v>
       </c>
       <c r="O25" t="n">
-        <v>-3.6515</v>
+        <v>-3.6151</v>
       </c>
       <c r="P25" t="n">
-        <v>5.679600000000001</v>
+        <v>5.690899999999999</v>
       </c>
       <c r="Q25" t="n">
-        <v>-13.6311</v>
+        <v>-13.658</v>
       </c>
       <c r="R25" t="n">
-        <v>19.3108</v>
+        <v>19.3489</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.5366000000000001</v>
+        <v>-0.5336999999999998</v>
       </c>
       <c r="T25" t="n">
-        <v>1.043</v>
+        <v>1.0186</v>
       </c>
       <c r="U25" t="n">
-        <v>-1.5798</v>
+        <v>-1.5523</v>
       </c>
       <c r="V25" t="n">
-        <v>-2.593399999999999</v>
+        <v>-2.5809</v>
       </c>
       <c r="W25" t="n">
-        <v>6.4802</v>
+        <v>6.4654</v>
       </c>
       <c r="X25" t="n">
-        <v>-9.073499999999999</v>
+        <v>-9.046199999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104726_W30.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104726_W30.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X25"/>
+  <dimension ref="A1:Y25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>0</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>0</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>-0.8603</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>-1.1984</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>-2.8326</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-0.1089</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-6.465299999999999</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>0.387</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.3155</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-1.2472</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-3.8132</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104726_W30.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,7 @@
       <c r="X25" t="n">
         <v>-9.046199999999999</v>
       </c>
+      <c r="Y25" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
